--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260716.xlsx
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
